--- a/WORD/3_22_07.xlsx
+++ b/WORD/3_22_07.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\WORD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF9680BB-175B-4EBC-AC4B-418E91820C7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B811F70B-20B8-4308-80EA-45A1B3FE2EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14820" yWindow="60" windowWidth="23580" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21060" yWindow="60" windowWidth="17340" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="281">
   <si>
     <t>Fre</t>
   </si>
@@ -676,6 +676,470 @@
   </si>
   <si>
     <t>不如；比不上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>劇的に</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>げきてきに</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>显著地；急剧地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>格別に</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>かくべつ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特别；格外</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>しんけん</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>真剣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>认真；严肃；真诚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>強大</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>きょうだい</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>到達</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>とうたつ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>到达；达成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>付属</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ふぞく</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>附属;附带;附设</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>接続</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>せつぞく</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>连接；接续；衔接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>みっちゃく</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>密着</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>紧密贴合；紧密连接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>取り払う</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>とりはらう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>清除；拆除；消除；去掉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>打ち消す</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>うちけす</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>否定；取消；消除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>締め切り</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>しめきり</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>截止日期；期限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>引き離す</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ひきはなす</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拉开；拉开距离；使分离</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ガイド</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>向导；指南；导游</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ツアー</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>旅游团；巡回演出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ごくごく</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>咕嘟咕嘟(喝水)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ぞろぞろ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成群结队；连续不断</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ぎしぎし</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嘎吱嘎吱（响）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>じめじめ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>潮湿；阴郁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ぶつかり合う</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>碰撞；冲突；相撞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>落ちる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>おちる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>落下；坠落；跌落</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>たまに</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>偶尔；有时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>何度か</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>なんどか</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>几次；若干次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>でたらめ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>胡说八道</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>悪口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>わるくち</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谩骂；说坏话;诽谤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>わがまま</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任性；自私</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>うそ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谎言；假话</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自慢</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自夸；吹嘘；炫耀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>さわがしい</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吵闹；喧嚣；嘈杂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>悲しい</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>かなしい</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>悲伤；悲哀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>温厚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>おんこう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>熱烈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ねつれつ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>热烈；热诚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>温かい</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>あたたかい</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>温暖；温和</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(为人)温和；敦厚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>濁る</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>にごる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>变浑浊；变模糊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>しばらく</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暂时；不久；好久</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>汚れる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>けがれる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弄脏；玷污；污损</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>好久；暂时；暂且</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>世代</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>せだい</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>世代；辈分；一代人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>年を取る</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>としをとる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>年纪增长；变老</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生活</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>せいかつ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日常生活；生存；生计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普及</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ふきゅう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>推广;传播;普及</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>うわさ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>传言，流言蜚语</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>流行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>りゅうこう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生じる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>しょうじる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)(植物)生成; (2)(事故、问题)发生、出现</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>出来る</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>できる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>能够；完成；发生；出现</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生まれる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>うまれる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>出生；产生；出现</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -728,15 +1192,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1005,639 +1472,1527 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E105"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="2" width="10.25" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
     <col min="4" max="4" width="15.125" customWidth="1"/>
-    <col min="5" max="5" width="16.5" customWidth="1"/>
+    <col min="5" max="5" width="29.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="1"/>
+      <c r="D2" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B3" s="1" t="s">
+      <c r="A3" s="1">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="C3" s="1"/>
+      <c r="D3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B4" s="1" t="s">
+      <c r="A4" s="1">
+        <v>0</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="C4" s="1"/>
+      <c r="D4" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B5" s="1" t="s">
+      <c r="A5" s="1">
+        <v>0</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="C5" s="1"/>
+      <c r="D5" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B6" s="1" t="s">
+      <c r="A6" s="1">
+        <v>0</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="C6" s="1"/>
+      <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B7" s="1" t="s">
+      <c r="A7" s="1">
+        <v>0</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="C7" s="1"/>
+      <c r="D7" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B8" s="1" t="s">
+      <c r="A8" s="1">
+        <v>0</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="C8" s="1"/>
+      <c r="D8" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B9" s="1" t="s">
+      <c r="A9" s="1">
+        <v>0</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="C9" s="1"/>
+      <c r="D9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B10" s="1" t="s">
+      <c r="A10" s="1">
+        <v>0</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="C10" s="1"/>
+      <c r="D10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B11" s="1" t="s">
+      <c r="A11" s="1">
+        <v>0</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="C11" s="1"/>
+      <c r="D11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="2" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B12" s="1" t="s">
+      <c r="A12" s="1">
+        <v>0</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="C12" s="1"/>
+      <c r="D12" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="2" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B13" s="1" t="s">
+      <c r="A13" s="1">
+        <v>0</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="C13" s="1"/>
+      <c r="D13" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B14" s="1" t="s">
+      <c r="A14" s="1">
+        <v>0</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="C14" s="1"/>
+      <c r="D14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B15" s="1" t="s">
+      <c r="A15" s="1">
+        <v>0</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="C15" s="1"/>
+      <c r="D15" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="2" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B16" s="1" t="s">
+      <c r="A16" s="1">
+        <v>0</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="C16" s="1"/>
+      <c r="D16" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B17" s="1" t="s">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A17" s="1">
+        <v>0</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="C17" s="1"/>
+      <c r="D17" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B18" s="1" t="s">
+      <c r="E17" s="1"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A18" s="1">
+        <v>0</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="C18" s="1"/>
+      <c r="D18" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B19" s="1" t="s">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A19" s="1">
+        <v>0</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="C19" s="1"/>
+      <c r="D19" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B20" s="1" t="s">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A20" s="1">
+        <v>0</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="C20" s="1"/>
+      <c r="D20" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B21" s="1" t="s">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A21" s="1">
+        <v>0</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="C21" s="1"/>
+      <c r="D21" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B22" s="1" t="s">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A22" s="1">
+        <v>0</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B23" s="1" t="s">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A23" s="1">
+        <v>0</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="C23" s="1"/>
+      <c r="D23" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B24" s="1" t="s">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A24" s="1">
+        <v>0</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="C24" s="1"/>
+      <c r="D24" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B25" s="1" t="s">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A25" s="1">
+        <v>0</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="C25" s="1"/>
+      <c r="D25" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B26" s="1" t="s">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A26" s="1">
+        <v>0</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="C26" s="1"/>
+      <c r="D26" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B27" s="1" t="s">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A27" s="1">
+        <v>0</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="C27" s="1"/>
+      <c r="D27" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B28" s="1" t="s">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A28" s="1">
+        <v>0</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="C28" s="1"/>
+      <c r="D28" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B29" s="1" t="s">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A29" s="1">
+        <v>0</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="C29" s="1"/>
+      <c r="D29" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B30" s="1" t="s">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A30" s="1">
+        <v>0</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="C30" s="1"/>
+      <c r="D30" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" s="2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B31" s="1" t="s">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A31" s="1">
+        <v>0</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="C31" s="1"/>
+      <c r="D31" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B32" s="1" t="s">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A32" s="1">
+        <v>0</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="C32" s="1"/>
+      <c r="D32" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B33" s="1" t="s">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A33" s="1">
+        <v>0</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="C33" s="1"/>
+      <c r="D33" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B34" s="1" t="s">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A34" s="1">
+        <v>0</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="C34" s="1"/>
+      <c r="D34" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B35" s="1" t="s">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A35" s="1">
+        <v>0</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="C35" s="1"/>
+      <c r="D35" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B36" s="1" t="s">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A36" s="1">
+        <v>0</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="C36" s="1"/>
+      <c r="D36" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E36" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B37" s="1" t="s">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A37" s="1">
+        <v>0</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="C37" s="1"/>
+      <c r="D37" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E37" s="2" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B38" s="1" t="s">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A38" s="1">
+        <v>0</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="C38" s="1"/>
+      <c r="D38" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" s="2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B39" s="1" t="s">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A39" s="1">
+        <v>0</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="C39" s="1"/>
+      <c r="D39" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E39" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B40" s="1" t="s">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A40" s="1">
+        <v>0</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="C40" s="1"/>
+      <c r="D40" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E40" s="2" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B41" s="1" t="s">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A41" s="1">
+        <v>0</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="C41" s="1"/>
+      <c r="D41" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" s="2" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B42" s="1" t="s">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A42" s="1">
+        <v>0</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="C42" s="1"/>
+      <c r="D42" s="2" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B43" s="1" t="s">
+      <c r="E42" s="1"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A43" s="1">
+        <v>0</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="C43" s="1"/>
+      <c r="D43" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E43" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B44" s="1" t="s">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A44" s="1">
+        <v>0</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="C44" s="1"/>
+      <c r="D44" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="E44" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B45" s="1" t="s">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A45" s="1">
+        <v>0</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="C45" s="1"/>
+      <c r="D45" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="E45" s="2" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B46" s="1" t="s">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A46" s="1">
+        <v>0</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="C46" s="1"/>
+      <c r="D46" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="E46" s="2" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B47" s="1" t="s">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A47" s="1">
+        <v>0</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="C47" s="1"/>
+      <c r="D47" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="E47" s="2" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B48" s="1" t="s">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A48" s="1">
+        <v>0</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="C48" s="1"/>
+      <c r="D48" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="E48" s="2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B49" s="1" t="s">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A49" s="1">
+        <v>0</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="C49" s="1"/>
+      <c r="D49" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E49" s="2" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B50" s="1" t="s">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A50" s="1">
+        <v>0</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="C50" s="1"/>
+      <c r="D50" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="E50" s="2" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B51" s="1" t="s">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A51" s="1">
+        <v>0</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="C51" s="1"/>
+      <c r="D51" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="E51" s="2" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B52" s="1" t="s">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A52" s="1">
+        <v>0</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="C52" s="1"/>
+      <c r="D52" s="2" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B53" s="1" t="s">
+      <c r="E52" s="1"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A53" s="1">
+        <v>0</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="C53" s="1"/>
+      <c r="D53" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="E53" s="2" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B54" s="1" t="s">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A54" s="1">
+        <v>0</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="C54" s="1"/>
+      <c r="D54" s="2" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B55" s="1" t="s">
+      <c r="E54" s="1"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A55" s="1">
+        <v>0</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="C55" s="1"/>
+      <c r="D55" s="2" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B56" s="1" t="s">
+      <c r="E55" s="1"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A56" s="1">
+        <v>0</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="C56" s="1"/>
+      <c r="D56" s="2" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B57" s="1" t="s">
+      <c r="E56" s="1"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A57" s="1">
+        <v>0</v>
+      </c>
+      <c r="B57" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="C57" s="1"/>
+      <c r="D57" s="2" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B58" s="1" t="s">
+      <c r="E57" s="1"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A58" s="1">
+        <v>0</v>
+      </c>
+      <c r="B58" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="C58" s="1"/>
+      <c r="D58" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="E58" s="2" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B59" s="1" t="s">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A59" s="1">
+        <v>0</v>
+      </c>
+      <c r="B59" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="C59" s="1"/>
+      <c r="D59" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="E59" s="1" t="s">
+      <c r="E59" s="2" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B60" s="1" t="s">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A60" s="1">
+        <v>0</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="C60" s="1"/>
+      <c r="D60" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="E60" s="2" t="s">
         <v>164</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A61" s="1">
+        <v>0</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C61" s="1"/>
+      <c r="D61" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A62" s="1">
+        <v>0</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A63" s="1">
+        <v>0</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C63" s="1"/>
+      <c r="D63" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A64" s="1">
+        <v>0</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C64" s="1"/>
+      <c r="D64" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E64" s="1"/>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A65" s="1">
+        <v>0</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C65" s="1"/>
+      <c r="D65" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A66" s="1">
+        <v>0</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A67" s="1">
+        <v>0</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C67" s="1"/>
+      <c r="D67" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A68" s="1">
+        <v>0</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C68" s="1"/>
+      <c r="D68" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A69" s="1">
+        <v>0</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C69" s="1"/>
+      <c r="D69" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A70" s="1">
+        <v>0</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A71" s="1">
+        <v>0</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C71" s="1"/>
+      <c r="D71" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A72" s="1">
+        <v>0</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C72" s="1"/>
+      <c r="D72" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A73" s="1">
+        <v>0</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A74" s="1">
+        <v>0</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A75" s="1">
+        <v>0</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A76" s="1">
+        <v>0</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A77" s="1">
+        <v>0</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A78" s="1">
+        <v>0</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A79" s="1">
+        <v>0</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A80" s="1">
+        <v>0</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C80" s="1"/>
+      <c r="D80" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A81" s="1">
+        <v>0</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A82" s="1">
+        <v>0</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C82" s="1"/>
+      <c r="D82" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A83" s="1">
+        <v>0</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A84" s="1">
+        <v>0</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C84" s="1"/>
+      <c r="D84" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A85" s="1">
+        <v>0</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C85" s="1"/>
+      <c r="D85" s="1"/>
+      <c r="E85" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A86" s="1">
+        <v>0</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C86" s="1"/>
+      <c r="D86" s="1"/>
+      <c r="E86" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A87" s="1">
+        <v>0</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C87" s="1"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A88" s="1">
+        <v>0</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C88" s="1"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A89" s="1">
+        <v>0</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C89" s="1"/>
+      <c r="D89" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A90" s="1">
+        <v>0</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C90" s="1"/>
+      <c r="D90" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A91" s="1">
+        <v>0</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C91" s="1"/>
+      <c r="D91" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A92" s="1">
+        <v>0</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C92" s="1"/>
+      <c r="D92" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A93" s="1">
+        <v>0</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C93" s="1"/>
+      <c r="D93" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A94" s="1">
+        <v>0</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C94" s="1"/>
+      <c r="D94" s="1"/>
+      <c r="E94" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A95" s="1">
+        <v>0</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C95" s="1"/>
+      <c r="D95" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A96" s="1">
+        <v>0</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C96" s="1"/>
+      <c r="D96" s="1"/>
+      <c r="E96" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A97" s="1">
+        <v>0</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C97" s="1"/>
+      <c r="D97" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A98" s="1">
+        <v>0</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C98" s="1"/>
+      <c r="D98" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A99" s="1">
+        <v>0</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C99" s="1"/>
+      <c r="D99" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A100" s="1">
+        <v>0</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C100" s="1"/>
+      <c r="D100" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A101" s="1">
+        <v>0</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C101" s="1"/>
+      <c r="D101" s="1"/>
+      <c r="E101" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A102" s="1">
+        <v>0</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C102" s="1"/>
+      <c r="D102" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="E102" s="1"/>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A103" s="1">
+        <v>0</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C103" s="1"/>
+      <c r="D103" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A104" s="1">
+        <v>0</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C104" s="1"/>
+      <c r="D104" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A105" s="1">
+        <v>0</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C105" s="1"/>
+      <c r="D105" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>280</v>
       </c>
     </row>
   </sheetData>
